--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/after_conversion_mdpi_tibet_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/after_conversion_mdpi_tibet_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="42">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Weixi–Qiaohou Fault</t>
@@ -500,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AE53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="21.7109375" customWidth="1"/>
@@ -522,9 +525,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,13 +619,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>26.4357</v>
@@ -672,12 +679,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3">
         <v>26.4357</v>
@@ -728,12 +735,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>26.4357</v>
@@ -784,12 +791,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5">
         <v>26.4357</v>
@@ -852,12 +859,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6">
         <v>26.2537</v>
@@ -908,12 +915,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>26.2537</v>
@@ -961,12 +968,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>26.2537</v>
@@ -1017,12 +1024,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>26.2537</v>
@@ -1073,12 +1080,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>26.2537</v>
@@ -1129,12 +1136,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>26.2537</v>
@@ -1185,12 +1192,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>26.2537</v>
@@ -1250,12 +1257,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>26.2519</v>
@@ -1306,12 +1313,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14">
         <v>26.2519</v>
@@ -1362,12 +1369,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15">
         <v>26.2519</v>
@@ -1418,12 +1425,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>26.2519</v>
@@ -1488,10 +1495,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17">
         <v>26.2392</v>
@@ -1541,10 +1548,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18">
         <v>26.2392</v>
@@ -1597,10 +1604,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19">
         <v>26.2392</v>
@@ -1653,10 +1660,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>26.2392</v>
@@ -1709,10 +1716,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C21">
         <v>26.2392</v>
@@ -1765,10 +1772,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22">
         <v>26.2392</v>
@@ -1821,10 +1828,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23">
         <v>26.2392</v>
@@ -1889,10 +1896,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24">
         <v>26.0843</v>
@@ -1942,10 +1949,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25">
         <v>26.0843</v>
@@ -1998,10 +2005,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26">
         <v>26.0843</v>
@@ -2054,10 +2061,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C27">
         <v>26.0843</v>
@@ -2110,10 +2117,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>26.0843</v>
@@ -2178,10 +2185,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>25.8047</v>
@@ -2234,10 +2241,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30">
         <v>25.8047</v>
@@ -2290,10 +2297,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>25.8047</v>
@@ -2346,10 +2353,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <v>25.8047</v>
@@ -2402,10 +2409,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33">
         <v>25.8047</v>
@@ -2458,10 +2465,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C34">
         <v>25.8047</v>
@@ -2526,10 +2533,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C35">
         <v>25.5697</v>
@@ -2579,10 +2586,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C36">
         <v>25.5697</v>
@@ -2635,10 +2642,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C37">
         <v>25.5697</v>
@@ -2691,10 +2698,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C38">
         <v>25.5697</v>
@@ -2747,10 +2754,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C39">
         <v>25.5697</v>
@@ -2803,10 +2810,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C40">
         <v>25.5697</v>
@@ -2871,10 +2878,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C41">
         <v>25.5697</v>
@@ -2927,10 +2934,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C42">
         <v>25.5621</v>
@@ -2983,10 +2990,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C43">
         <v>3.87</v>
@@ -3027,10 +3034,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C44">
         <v>3.85</v>
@@ -3071,10 +3078,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C45">
         <v>3.45</v>
@@ -3115,10 +3122,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C46">
         <v>3.45</v>
@@ -3183,10 +3190,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C47">
         <v>25.1706</v>
@@ -3236,10 +3243,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C48">
         <v>25.1706</v>
@@ -3289,10 +3296,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C49">
         <v>25.1706</v>
@@ -3345,10 +3352,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C50">
         <v>25.1706</v>
@@ -3401,10 +3408,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C51">
         <v>25.1706</v>
@@ -3457,10 +3464,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C52">
         <v>25.1706</v>
@@ -3525,10 +3532,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L53">
         <v>13.79997500681053</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/after_conversion_mdpi_tibet_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/after_conversion_mdpi_tibet_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="43">
   <si>
     <t>location</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>XQC</t>
+  </si>
+  <si>
+    <t>Metamorphic Rock</t>
   </si>
 </sst>
 </file>
@@ -510,7 +513,7 @@
     <col min="3" max="3" width="16.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" customWidth="1"/>
@@ -636,6 +639,9 @@
       <c r="D2">
         <v>99.6268</v>
       </c>
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
       <c r="H2">
         <v>34</v>
       </c>
@@ -692,6 +698,9 @@
       <c r="D3">
         <v>99.6268</v>
       </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
       <c r="H3">
         <v>34</v>
       </c>
@@ -748,6 +757,9 @@
       <c r="D4">
         <v>99.6268</v>
       </c>
+      <c r="F4" t="s">
+        <v>42</v>
+      </c>
       <c r="H4">
         <v>34</v>
       </c>
@@ -804,6 +816,9 @@
       <c r="D5">
         <v>99.6268</v>
       </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
       <c r="H5">
         <v>34</v>
       </c>
@@ -872,6 +887,9 @@
       <c r="D6">
         <v>99.9877</v>
       </c>
+      <c r="F6" t="s">
+        <v>42</v>
+      </c>
       <c r="H6">
         <v>78</v>
       </c>
@@ -928,6 +946,9 @@
       <c r="D7">
         <v>99.9877</v>
       </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
       <c r="H7">
         <v>78</v>
       </c>
@@ -981,6 +1002,9 @@
       <c r="D8">
         <v>99.9877</v>
       </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
       <c r="H8">
         <v>78</v>
       </c>
@@ -1037,6 +1061,9 @@
       <c r="D9">
         <v>99.9877</v>
       </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
       <c r="H9">
         <v>78</v>
       </c>
@@ -1093,6 +1120,9 @@
       <c r="D10">
         <v>99.9877</v>
       </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
       <c r="H10">
         <v>78</v>
       </c>
@@ -1149,6 +1179,9 @@
       <c r="D11">
         <v>99.9877</v>
       </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
       <c r="H11">
         <v>78</v>
       </c>
@@ -1205,6 +1238,9 @@
       <c r="D12">
         <v>99.9877</v>
       </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
       <c r="H12">
         <v>78</v>
       </c>
@@ -1270,6 +1306,9 @@
       <c r="D13">
         <v>99.9913</v>
       </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
       <c r="H13">
         <v>72</v>
       </c>
@@ -1326,6 +1365,9 @@
       <c r="D14">
         <v>99.9913</v>
       </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
       <c r="H14">
         <v>72</v>
       </c>
@@ -1382,6 +1424,9 @@
       <c r="D15">
         <v>99.9913</v>
       </c>
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
       <c r="H15">
         <v>72</v>
       </c>
@@ -1438,6 +1483,9 @@
       <c r="D16">
         <v>99.9913</v>
       </c>
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
       <c r="H16">
         <v>72</v>
       </c>
@@ -1506,6 +1554,9 @@
       <c r="D17">
         <v>99.9926</v>
       </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
       <c r="H17">
         <v>74</v>
       </c>
@@ -1559,6 +1610,9 @@
       <c r="D18">
         <v>99.9926</v>
       </c>
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
       <c r="H18">
         <v>74</v>
       </c>
@@ -1615,6 +1669,9 @@
       <c r="D19">
         <v>99.9926</v>
       </c>
+      <c r="F19" t="s">
+        <v>42</v>
+      </c>
       <c r="H19">
         <v>74</v>
       </c>
@@ -1671,6 +1728,9 @@
       <c r="D20">
         <v>99.9926</v>
       </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
       <c r="H20">
         <v>74</v>
       </c>
@@ -1727,6 +1787,9 @@
       <c r="D21">
         <v>99.9926</v>
       </c>
+      <c r="F21" t="s">
+        <v>42</v>
+      </c>
       <c r="H21">
         <v>74</v>
       </c>
@@ -1783,6 +1846,9 @@
       <c r="D22">
         <v>99.9926</v>
       </c>
+      <c r="F22" t="s">
+        <v>42</v>
+      </c>
       <c r="H22">
         <v>74</v>
       </c>
@@ -1839,6 +1905,9 @@
       <c r="D23">
         <v>99.9926</v>
       </c>
+      <c r="F23" t="s">
+        <v>42</v>
+      </c>
       <c r="H23">
         <v>74</v>
       </c>
@@ -1907,6 +1976,9 @@
       <c r="D24">
         <v>100.0252</v>
       </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
       <c r="H24">
         <v>92</v>
       </c>
@@ -1960,6 +2032,9 @@
       <c r="D25">
         <v>100.0252</v>
       </c>
+      <c r="F25" t="s">
+        <v>42</v>
+      </c>
       <c r="H25">
         <v>92</v>
       </c>
@@ -2016,6 +2091,9 @@
       <c r="D26">
         <v>100.0252</v>
       </c>
+      <c r="F26" t="s">
+        <v>42</v>
+      </c>
       <c r="H26">
         <v>92</v>
       </c>
@@ -2072,6 +2150,9 @@
       <c r="D27">
         <v>100.0252</v>
       </c>
+      <c r="F27" t="s">
+        <v>42</v>
+      </c>
       <c r="H27">
         <v>92</v>
       </c>
@@ -2128,6 +2209,9 @@
       <c r="D28">
         <v>100.0252</v>
       </c>
+      <c r="F28" t="s">
+        <v>42</v>
+      </c>
       <c r="H28">
         <v>92</v>
       </c>
@@ -2196,6 +2280,9 @@
       <c r="D29">
         <v>99.9204</v>
       </c>
+      <c r="F29" t="s">
+        <v>42</v>
+      </c>
       <c r="H29">
         <v>70</v>
       </c>
@@ -2252,6 +2339,9 @@
       <c r="D30">
         <v>99.9204</v>
       </c>
+      <c r="F30" t="s">
+        <v>42</v>
+      </c>
       <c r="H30">
         <v>70</v>
       </c>
@@ -2308,6 +2398,9 @@
       <c r="D31">
         <v>99.9204</v>
       </c>
+      <c r="F31" t="s">
+        <v>42</v>
+      </c>
       <c r="H31">
         <v>70</v>
       </c>
@@ -2364,6 +2457,9 @@
       <c r="D32">
         <v>99.9204</v>
       </c>
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
       <c r="H32">
         <v>70</v>
       </c>
@@ -2420,6 +2516,9 @@
       <c r="D33">
         <v>99.9204</v>
       </c>
+      <c r="F33" t="s">
+        <v>42</v>
+      </c>
       <c r="H33">
         <v>70</v>
       </c>
@@ -2476,6 +2575,9 @@
       <c r="D34">
         <v>99.9204</v>
       </c>
+      <c r="F34" t="s">
+        <v>42</v>
+      </c>
       <c r="H34">
         <v>70</v>
       </c>
@@ -2544,6 +2646,9 @@
       <c r="D35">
         <v>100.1822</v>
       </c>
+      <c r="F35" t="s">
+        <v>42</v>
+      </c>
       <c r="H35">
         <v>78</v>
       </c>
@@ -2597,6 +2702,9 @@
       <c r="D36">
         <v>100.1822</v>
       </c>
+      <c r="F36" t="s">
+        <v>42</v>
+      </c>
       <c r="H36">
         <v>78</v>
       </c>
@@ -2653,6 +2761,9 @@
       <c r="D37">
         <v>100.1822</v>
       </c>
+      <c r="F37" t="s">
+        <v>42</v>
+      </c>
       <c r="H37">
         <v>78</v>
       </c>
@@ -2709,6 +2820,9 @@
       <c r="D38">
         <v>100.1822</v>
       </c>
+      <c r="F38" t="s">
+        <v>42</v>
+      </c>
       <c r="H38">
         <v>78</v>
       </c>
@@ -2765,6 +2879,9 @@
       <c r="D39">
         <v>100.1822</v>
       </c>
+      <c r="F39" t="s">
+        <v>42</v>
+      </c>
       <c r="H39">
         <v>78</v>
       </c>
@@ -2821,6 +2938,9 @@
       <c r="D40">
         <v>100.1822</v>
       </c>
+      <c r="F40" t="s">
+        <v>42</v>
+      </c>
       <c r="H40">
         <v>78</v>
       </c>
@@ -2889,6 +3009,9 @@
       <c r="D41">
         <v>100.1822</v>
       </c>
+      <c r="F41" t="s">
+        <v>42</v>
+      </c>
       <c r="H41">
         <v>78</v>
       </c>
@@ -2945,6 +3068,9 @@
       <c r="D42">
         <v>100.1299</v>
       </c>
+      <c r="F42" t="s">
+        <v>42</v>
+      </c>
       <c r="H42">
         <v>63</v>
       </c>
@@ -3001,6 +3127,9 @@
       <c r="D43">
         <v>92.16</v>
       </c>
+      <c r="F43" t="s">
+        <v>42</v>
+      </c>
       <c r="H43">
         <v>1</v>
       </c>
@@ -3045,6 +3174,9 @@
       <c r="D44">
         <v>96.59999999999999</v>
       </c>
+      <c r="F44" t="s">
+        <v>42</v>
+      </c>
       <c r="H44">
         <v>0.99</v>
       </c>
@@ -3089,6 +3221,9 @@
       <c r="D45">
         <v>92.95999999999999</v>
       </c>
+      <c r="F45" t="s">
+        <v>42</v>
+      </c>
       <c r="H45">
         <v>1.07</v>
       </c>
@@ -3133,6 +3268,9 @@
       <c r="D46">
         <v>92.95999999999999</v>
       </c>
+      <c r="F46" t="s">
+        <v>42</v>
+      </c>
       <c r="H46">
         <v>1.07</v>
       </c>
@@ -3201,6 +3339,9 @@
       <c r="D47">
         <v>100.323</v>
       </c>
+      <c r="F47" t="s">
+        <v>42</v>
+      </c>
       <c r="H47">
         <v>46</v>
       </c>
@@ -3254,6 +3395,9 @@
       <c r="D48">
         <v>100.323</v>
       </c>
+      <c r="F48" t="s">
+        <v>42</v>
+      </c>
       <c r="H48">
         <v>46</v>
       </c>
@@ -3307,6 +3451,9 @@
       <c r="D49">
         <v>100.323</v>
       </c>
+      <c r="F49" t="s">
+        <v>42</v>
+      </c>
       <c r="H49">
         <v>46</v>
       </c>
@@ -3363,6 +3510,9 @@
       <c r="D50">
         <v>100.323</v>
       </c>
+      <c r="F50" t="s">
+        <v>42</v>
+      </c>
       <c r="H50">
         <v>46</v>
       </c>
@@ -3419,6 +3569,9 @@
       <c r="D51">
         <v>100.323</v>
       </c>
+      <c r="F51" t="s">
+        <v>42</v>
+      </c>
       <c r="H51">
         <v>46</v>
       </c>
@@ -3475,6 +3628,9 @@
       <c r="D52">
         <v>100.323</v>
       </c>
+      <c r="F52" t="s">
+        <v>42</v>
+      </c>
       <c r="H52">
         <v>46</v>
       </c>
@@ -3536,6 +3692,9 @@
       </c>
       <c r="B53" t="s">
         <v>41</v>
+      </c>
+      <c r="F53" t="s">
+        <v>42</v>
       </c>
       <c r="L53">
         <v>13.79997500681053</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/after_conversion_mdpi_tibet_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/MDPI_Tibet_Datenbank/after_conversion_mdpi_tibet_mapped_readable.xlsx
@@ -517,7 +517,7 @@
     <col min="7" max="7" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="18.7109375" customWidth="1"/>
     <col min="9" max="9" width="38.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" customWidth="1"/>
     <col min="11" max="11" width="23.7109375" customWidth="1"/>
     <col min="12" max="12" width="34.7109375" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" customWidth="1"/>
@@ -900,7 +900,7 @@
         <v>8.24</v>
       </c>
       <c r="L6">
-        <v>15.76651471811327</v>
+        <v>26.0441969630032</v>
       </c>
       <c r="N6">
         <v>10.1071045994416</v>
@@ -918,7 +918,7 @@
         <v>1.579013116801999</v>
       </c>
       <c r="S6">
-        <v>0.0116151289480929</v>
+        <v>10.28929737383802</v>
       </c>
       <c r="U6">
         <v>0.8900642738942612</v>
@@ -959,7 +959,7 @@
         <v>8.24</v>
       </c>
       <c r="L7">
-        <v>14.01676797810735</v>
+        <v>23.55780630711544</v>
       </c>
       <c r="N7">
         <v>11.4811940911629</v>
@@ -974,7 +974,10 @@
         <v>0.4211565585331452</v>
       </c>
       <c r="R7">
-        <v>0.0448677909639808</v>
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>9.516395484522294</v>
       </c>
       <c r="U7">
         <v>0.2225160684735653</v>
@@ -983,7 +986,7 @@
         <v>221.0759027266028</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.0695106354497789</v>
       </c>
       <c r="AD7">
         <v>1</v>
@@ -1251,7 +1254,7 @@
         <v>8.24</v>
       </c>
       <c r="L12">
-        <v>15.33945686688352</v>
+        <v>25.83197695971041</v>
       </c>
       <c r="N12">
         <v>9.133628093435824</v>
@@ -1268,6 +1271,9 @@
       <c r="R12">
         <v>1.559442015407037</v>
       </c>
+      <c r="S12">
+        <v>10.49252009282689</v>
+      </c>
       <c r="T12">
         <v>0.1649855907780979</v>
       </c>
@@ -1567,7 +1573,7 @@
         <v>6.91</v>
       </c>
       <c r="L17">
-        <v>18.48176705297896</v>
+        <v>18.4703342952453</v>
       </c>
       <c r="N17">
         <v>12.78786228778549</v>
@@ -1584,6 +1590,9 @@
       <c r="R17">
         <v>2.188007495315428</v>
       </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
       <c r="U17">
         <v>1.133041590043557</v>
       </c>
@@ -1591,7 +1600,7 @@
         <v>357.9324139383093</v>
       </c>
       <c r="AA17">
-        <v>0.0114327577336629</v>
+        <v>0</v>
       </c>
       <c r="AD17">
         <v>1</v>
@@ -1989,7 +1998,7 @@
         <v>8.130000000000001</v>
       </c>
       <c r="L24">
-        <v>15.84833630672409</v>
+        <v>15.91133866081134</v>
       </c>
       <c r="N24">
         <v>7.211903695074101</v>
@@ -2006,6 +2015,9 @@
       <c r="R24">
         <v>2.487091401207579</v>
       </c>
+      <c r="S24">
+        <v>3.95350133078103</v>
+      </c>
       <c r="U24">
         <v>0.457820416744462</v>
       </c>
@@ -2013,7 +2025,7 @@
         <v>358.9851563322455</v>
       </c>
       <c r="AA24">
-        <v>3.890498976693777</v>
+        <v>0</v>
       </c>
       <c r="AD24">
         <v>1</v>
@@ -2659,7 +2671,7 @@
         <v>7.4</v>
       </c>
       <c r="L35">
-        <v>27.1419163497648</v>
+        <v>27.28730780396549</v>
       </c>
       <c r="N35">
         <v>11.93313425637291</v>
@@ -2676,6 +2688,9 @@
       <c r="R35">
         <v>3.172912762856548</v>
       </c>
+      <c r="S35">
+        <v>9.123552857573651</v>
+      </c>
       <c r="U35">
         <v>0.4798162579958719</v>
       </c>
@@ -2683,7 +2698,7 @@
         <v>353.1950731655963</v>
       </c>
       <c r="AA35">
-        <v>8.97816140337296</v>
+        <v>0</v>
       </c>
       <c r="AD35">
         <v>1</v>
@@ -3122,40 +3137,52 @@
         <v>39</v>
       </c>
       <c r="C43">
-        <v>3.87</v>
+        <v>25.5621</v>
       </c>
       <c r="D43">
-        <v>92.16</v>
+        <v>100.1299</v>
       </c>
       <c r="F43" t="s">
         <v>42</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="I43">
-        <v>5.19</v>
+        <v>471</v>
       </c>
       <c r="J43">
-        <v>10.98</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L43">
-        <v>10.55644457807197</v>
+        <v>8.252648200904737</v>
       </c>
       <c r="N43">
-        <v>0.1874746979841337</v>
+        <v>4.008739713739621</v>
       </c>
       <c r="O43">
+        <v>0.0411437975725159</v>
+      </c>
+      <c r="P43">
+        <v>0.2739657667548281</v>
+      </c>
+      <c r="Q43">
+        <v>0.1215796897038081</v>
+      </c>
+      <c r="R43">
+        <v>0.8790339371226317</v>
+      </c>
+      <c r="S43">
+        <v>2.556017359153544</v>
+      </c>
+      <c r="U43">
+        <v>0.09898128563134451</v>
+      </c>
+      <c r="Z43">
+        <v>273.1866512264449</v>
+      </c>
+      <c r="AA43">
         <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>2.159684692173317</v>
-      </c>
-      <c r="Z43">
-        <v>8209.285187914516</v>
       </c>
       <c r="AD43">
         <v>1</v>
@@ -3169,40 +3196,52 @@
         <v>39</v>
       </c>
       <c r="C44">
-        <v>3.85</v>
+        <v>25.5621</v>
       </c>
       <c r="D44">
-        <v>96.59999999999999</v>
+        <v>100.1299</v>
       </c>
       <c r="F44" t="s">
         <v>42</v>
       </c>
       <c r="H44">
-        <v>0.99</v>
+        <v>63</v>
       </c>
       <c r="I44">
-        <v>6.21</v>
+        <v>471</v>
       </c>
       <c r="J44">
-        <v>12.93</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L44">
-        <v>12.1811049990346</v>
+        <v>9.04752650992269</v>
       </c>
       <c r="N44">
-        <v>0.1635510126265296</v>
+        <v>4.201869100990097</v>
       </c>
       <c r="O44">
-        <v>0.0785846533635054</v>
+        <v>0.0407323595967907</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>0.3226208892659314</v>
+      </c>
+      <c r="Q44">
+        <v>0.1060648801128349</v>
+      </c>
+      <c r="R44">
+        <v>0.8628981886321049</v>
+      </c>
+      <c r="S44">
+        <v>3.057190806466416</v>
       </c>
       <c r="U44">
-        <v>2.12004102480159</v>
+        <v>0.0984697544394513</v>
       </c>
       <c r="Z44">
-        <v>9818.928308242972</v>
+        <v>326.8765133171913</v>
+      </c>
+      <c r="AA44">
+        <v>0.0308040171018742</v>
       </c>
       <c r="AD44">
         <v>1</v>
@@ -3216,40 +3255,52 @@
         <v>39</v>
       </c>
       <c r="C45">
-        <v>3.45</v>
+        <v>25.5621</v>
       </c>
       <c r="D45">
-        <v>92.95999999999999</v>
+        <v>100.1299</v>
       </c>
       <c r="F45" t="s">
         <v>42</v>
       </c>
       <c r="H45">
-        <v>1.07</v>
+        <v>63</v>
       </c>
       <c r="I45">
-        <v>5.81</v>
+        <v>471</v>
       </c>
       <c r="J45">
-        <v>12.63</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L45">
-        <v>7.253213978002612</v>
+        <v>6.984542818025049</v>
       </c>
       <c r="N45">
-        <v>0.1726855106721603</v>
+        <v>4.043537801532499</v>
       </c>
       <c r="O45">
-        <v>0.0065830076116025</v>
+        <v>0.044023863402592</v>
       </c>
       <c r="P45">
-        <v>1.080892260092819</v>
+        <v>0.3151354858026847</v>
+      </c>
+      <c r="Q45">
+        <v>0.1119887165021156</v>
+      </c>
+      <c r="R45">
+        <v>0.8817405788049136</v>
+      </c>
+      <c r="S45">
+        <v>1.191475134716996</v>
       </c>
       <c r="U45">
-        <v>2.166334597667929</v>
+        <v>0.0882391306015862</v>
       </c>
       <c r="Z45">
-        <v>3826.718601958101</v>
+        <v>305.8216654384672</v>
+      </c>
+      <c r="AA45">
+        <v>0.0025804412231936</v>
       </c>
       <c r="AD45">
         <v>1</v>
@@ -3263,22 +3314,22 @@
         <v>39</v>
       </c>
       <c r="C46">
-        <v>3.45</v>
+        <v>25.5621</v>
       </c>
       <c r="D46">
-        <v>92.95999999999999</v>
+        <v>100.1299</v>
       </c>
       <c r="F46" t="s">
         <v>42</v>
       </c>
       <c r="H46">
-        <v>1.07</v>
+        <v>63</v>
       </c>
       <c r="I46">
-        <v>5.81</v>
+        <v>471</v>
       </c>
       <c r="J46">
-        <v>12.63</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L46">
         <v>8.934419422921966</v>
@@ -3352,7 +3403,7 @@
         <v>7.32</v>
       </c>
       <c r="L47">
-        <v>81.92017731391307</v>
+        <v>82.38138755788481</v>
       </c>
       <c r="N47">
         <v>41.95083473870486</v>
@@ -3369,6 +3420,9 @@
       <c r="R47">
         <v>7.241723922548407</v>
       </c>
+      <c r="S47">
+        <v>28.94170130193652</v>
+      </c>
       <c r="U47">
         <v>0.4905584130256302</v>
       </c>
@@ -3376,7 +3430,7 @@
         <v>298.9788398778819</v>
       </c>
       <c r="AA47">
-        <v>28.48049105796478</v>
+        <v>0</v>
       </c>
       <c r="AD47">
         <v>1</v>
@@ -3408,7 +3462,7 @@
         <v>7.32</v>
       </c>
       <c r="L48">
-        <v>54.55722377878762</v>
+        <v>84.49406084661157</v>
       </c>
       <c r="N48">
         <v>42.82165688572165</v>
@@ -3425,6 +3479,9 @@
       <c r="R48">
         <v>7.490214449302519</v>
       </c>
+      <c r="S48">
+        <v>29.93683706782394</v>
+      </c>
       <c r="U48">
         <v>0.4946506625607763</v>
       </c>
@@ -3693,35 +3750,44 @@
       <c r="B53" t="s">
         <v>41</v>
       </c>
+      <c r="C53">
+        <v>25.4829</v>
+      </c>
+      <c r="D53">
+        <v>99.79040000000001</v>
+      </c>
       <c r="F53" t="s">
         <v>42</v>
       </c>
+      <c r="H53">
+        <v>56</v>
+      </c>
       <c r="L53">
-        <v>13.79997500681053</v>
+        <v>20.32098573309655</v>
       </c>
       <c r="N53">
-        <v>4.340643875108097</v>
+        <v>6.603807110893546</v>
       </c>
       <c r="O53">
-        <v>2.304052664060893</v>
+        <v>0.3805801275457725</v>
       </c>
       <c r="P53">
-        <v>3.788113179300364</v>
+        <v>1.730874794151405</v>
       </c>
       <c r="Q53">
-        <v>0.2609308885754584</v>
+        <v>0.5136812411847672</v>
       </c>
       <c r="R53">
-        <v>0.7221528211534458</v>
+        <v>0.4563814282739954</v>
       </c>
       <c r="S53">
-        <v>0.7184906451993549</v>
+        <v>9.882524157281273</v>
       </c>
       <c r="T53">
         <v>0.0288184438040345</v>
       </c>
       <c r="U53">
-        <v>0.6517649104948297</v>
+        <v>0.3790446131929009</v>
       </c>
       <c r="V53">
         <v>143.0495320703036</v>
@@ -3733,10 +3799,10 @@
         <v>0.000589755724635</v>
       </c>
       <c r="Z53">
-        <v>780.082113906727</v>
+        <v>200.0210548478787</v>
       </c>
       <c r="AA53">
-        <v>0.0612854790508492</v>
+        <v>0.001612775764496</v>
       </c>
       <c r="AD53">
         <v>1</v>
